--- a/kawasaki_project/05_試算・管理シート/川崎町_策定委員会_逆算工程表_R8.10.20.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_策定委員会_逆算工程表_R8.10.20.xlsx
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>⚠ **12月29日に当たります。** 年末年始を挟むため、令和9年1月4日（月）開始とする案を併記します（その場合の納品は3月15日ちょうどになります）</t>
+          <t>⚠ **12月29日に当たります。** 年末年始を挟むため、令和9年1月4日（月）開始とする案を併記します（その場合、後続の工程が6日ずつ遅れ、案Ⅰの納品は令和9年3月16日（火）となり納期を1日超えます。案Ⅱ（印刷2週間）なら令和9年3月9日（火））</t>
         </is>
       </c>
     </row>
